--- a/PPREstimation/output/top10/52_2_Sea_of_Okhotsk_SD_(1980).xlsx
+++ b/PPREstimation/output/top10/52_2_Sea_of_Okhotsk_SD_(1980).xlsx
@@ -617,7 +617,6 @@
           <t>Import</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr"/>
       <c r="F2" s="2" t="n">
         <v>1</v>
       </c>
@@ -640,10 +639,10 @@
         <v>0</v>
       </c>
       <c r="M2" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O2" s="2" t="n">
         <v>0</v>
@@ -701,7 +700,6 @@
           <t>DET</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr"/>
       <c r="F3" s="2" t="n">
         <v>1</v>
       </c>
@@ -785,7 +783,6 @@
           <t>Regular</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
       <c r="F4" s="2" t="n">
         <v>3.680006580592298</v>
       </c>
@@ -869,7 +866,6 @@
           <t>Regular</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
       <c r="F5" s="2" t="n">
         <v>3.605340120582676</v>
       </c>
@@ -953,7 +949,6 @@
           <t>Regular</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr"/>
       <c r="F6" s="2" t="n">
         <v>3.299</v>
       </c>
@@ -1037,7 +1032,6 @@
           <t>Regular</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr"/>
       <c r="F7" s="2" t="n">
         <v>2.299</v>
       </c>
@@ -1121,7 +1115,6 @@
           <t>Regular</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr"/>
       <c r="F8" s="2" t="n">
         <v>3.370962699341109</v>
       </c>
@@ -1205,7 +1198,6 @@
           <t>Regular</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr"/>
       <c r="F9" s="2" t="n">
         <v>3.1978287092883</v>
       </c>
@@ -1289,7 +1281,6 @@
           <t>Regular</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr"/>
       <c r="F10" s="2" t="n">
         <v>2</v>
       </c>
@@ -1373,7 +1364,6 @@
           <t>PP</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr"/>
       <c r="F11" s="2" t="n">
         <v>1</v>
       </c>
@@ -1449,7 +1439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V11"/>
+  <dimension ref="A1:X11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -1587,6 +1577,16 @@
           <t>MC_new_TE_EEfix</t>
         </is>
       </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>SPPR_1995_TEmean_catch</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>Ulanowicz_globalTEmean_catch</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
@@ -1597,9 +1597,6 @@
           <t>diet_import</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
       <c r="F2" s="2" t="n">
         <v>0</v>
       </c>
@@ -1630,19 +1627,19 @@
       <c r="O2" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="P2" t="inlineStr"/>
       <c r="Q2" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="R2" t="inlineStr"/>
       <c r="S2" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="T2" t="inlineStr"/>
       <c r="U2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="V2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1655,9 +1652,6 @@
           <t>Detritus</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
       <c r="F3" s="2" t="n">
         <v>0</v>
       </c>
@@ -1707,6 +1701,9 @@
         <v>0</v>
       </c>
       <c r="V3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1719,11 +1716,8 @@
           <t>Mammals and birds</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
       <c r="F4" s="2" t="n">
-        <v>48.18043942955434</v>
+        <v>67.66369465845605</v>
       </c>
       <c r="G4" s="2" t="n">
         <v>0</v>
@@ -1731,7 +1725,6 @@
       <c r="H4" s="2" t="n">
         <v>20.44541946620081</v>
       </c>
-      <c r="I4" t="inlineStr"/>
       <c r="J4" s="2" t="n">
         <v>0</v>
       </c>
@@ -1770,6 +1763,9 @@
       </c>
       <c r="V4" s="2" t="n">
         <v>0</v>
+      </c>
+      <c r="X4" t="n">
+        <v>71.20850372013344</v>
       </c>
     </row>
     <row r="5">
@@ -1781,11 +1777,8 @@
           <t>Nectobenthos</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
       <c r="F5" s="2" t="n">
-        <v>32.98942136158241</v>
+        <v>46.71486371866341</v>
       </c>
       <c r="G5" s="2" t="n">
         <v>794.0613257489242</v>
@@ -1834,6 +1827,9 @@
       </c>
       <c r="V5" s="2" t="n">
         <v>26947.97573917317</v>
+      </c>
+      <c r="X5" t="n">
+        <v>49.21670440158326</v>
       </c>
     </row>
     <row r="6">
@@ -1845,11 +1841,8 @@
           <t>Predatory zoobenthos</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
       <c r="F6" s="2" t="n">
-        <v>16.84141275334834</v>
+        <v>22.74251350402013</v>
       </c>
       <c r="G6" s="2" t="n">
         <v>153.4693810067471</v>
@@ -1898,6 +1891,9 @@
       </c>
       <c r="V6" s="2" t="n">
         <v>163.9617961193308</v>
+      </c>
+      <c r="X6" t="n">
+        <v>23.78566475037847</v>
       </c>
     </row>
     <row r="7">
@@ -1909,11 +1905,8 @@
           <t>Non-predatory zoobenthos</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
       <c r="F7" s="2" t="n">
-        <v>3.614884905709641</v>
+        <v>4.41639356765216</v>
       </c>
       <c r="G7" s="2" t="n">
         <v>3.85429558696389</v>
@@ -1962,6 +1955,9 @@
       </c>
       <c r="V7" s="2" t="n">
         <v>4.021840113462793</v>
+      </c>
+      <c r="X7" t="n">
+        <v>4.550428800158525</v>
       </c>
     </row>
     <row r="8">
@@ -1973,11 +1969,8 @@
           <t>Necton</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
       <c r="F8" s="2" t="n">
-        <v>18.89248698205429</v>
+        <v>24.42180522907254</v>
       </c>
       <c r="G8" s="2" t="n">
         <v>40.27526191934068</v>
@@ -2026,6 +2019,9 @@
       </c>
       <c r="V8" s="2" t="n">
         <v>1197.692607212351</v>
+      </c>
+      <c r="X8" t="n">
+        <v>25.38130195482818</v>
       </c>
     </row>
     <row r="9">
@@ -2037,11 +2033,8 @@
           <t>Predatory plankton</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
       <c r="F9" s="2" t="n">
-        <v>9.93791101168336</v>
+        <v>12.14138967428119</v>
       </c>
       <c r="G9" s="2" t="n">
         <v>12.50294208253858</v>
@@ -2090,6 +2083,9 @@
       </c>
       <c r="V9" s="2" t="n">
         <v>209.5592222512306</v>
+      </c>
+      <c r="X9" t="n">
+        <v>12.5098744940813</v>
       </c>
     </row>
     <row r="10">
@@ -2101,11 +2097,8 @@
           <t>Herbivorous plankton</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
       <c r="F10" s="2" t="n">
-        <v>2.595011223953063</v>
+        <v>2.868308683927719</v>
       </c>
       <c r="G10" s="2" t="n">
         <v>2.810627092006287</v>
@@ -2155,6 +2148,9 @@
       <c r="V10" s="2" t="n">
         <v>2.875704343664626</v>
       </c>
+      <c r="X10" t="n">
+        <v>2.911509189089886</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
@@ -2165,9 +2161,6 @@
           <t>Phytoplankton</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
       <c r="F11" s="2" t="n">
         <v>1</v>
       </c>
@@ -2217,6 +2210,9 @@
         <v>1</v>
       </c>
       <c r="V11" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="X11" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2231,7 +2227,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V11"/>
+  <dimension ref="A1:X11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -2369,6 +2365,16 @@
           <t>MC_new_TE_EEfix</t>
         </is>
       </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>SPPR_1995_TEmean_catch</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>Ulanowicz_globalTEmean_catch</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
@@ -2418,19 +2424,22 @@
       <c r="O2" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="P2" t="inlineStr"/>
       <c r="Q2" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="R2" t="inlineStr"/>
       <c r="S2" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="T2" t="inlineStr"/>
       <c r="U2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="V2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1</v>
+      </c>
+      <c r="X2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2503,6 +2512,12 @@
       <c r="V3" s="2" t="n">
         <v>0.8537152806236192</v>
       </c>
+      <c r="W3" t="n">
+        <v>1</v>
+      </c>
+      <c r="X3" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
@@ -2520,10 +2535,10 @@
         <v>416.179587813214</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>56.28900254449202</v>
+        <v>73.16902902025888</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>88.59793106865003</v>
+        <v>124.051602358648</v>
       </c>
       <c r="G4" s="2" t="n">
         <v>0</v>
@@ -2531,7 +2546,6 @@
       <c r="H4" s="2" t="n">
         <v>37.16743582727102</v>
       </c>
-      <c r="I4" t="inlineStr"/>
       <c r="J4" s="2" t="n">
         <v>0</v>
       </c>
@@ -2570,6 +2584,12 @@
       </c>
       <c r="V4" s="2" t="n">
         <v>0</v>
+      </c>
+      <c r="W4" t="n">
+        <v>76.0908418656785</v>
+      </c>
+      <c r="X4" t="n">
+        <v>130.495353702711</v>
       </c>
     </row>
     <row r="5">
@@ -2588,10 +2608,10 @@
         <v>357.8589689857071</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>50.88677450113939</v>
+        <v>65.71390752353284</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>78.79467664999078</v>
+        <v>109.0006292271502</v>
       </c>
       <c r="G5" s="2" t="n">
         <v>1974.676817436918</v>
@@ -2640,6 +2660,12 @@
       </c>
       <c r="V5" s="2" t="n">
         <v>50303.53156474263</v>
+      </c>
+      <c r="W5" t="n">
+        <v>68.27106823443432</v>
+      </c>
+      <c r="X5" t="n">
+        <v>114.4546145406711</v>
       </c>
     </row>
     <row r="6">
@@ -2658,10 +2684,10 @@
         <v>199.0673338987186</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>34.38626616103237</v>
+        <v>43.28733232006891</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>45.45142535053177</v>
+        <v>59.41950984806437</v>
       </c>
       <c r="G6" s="2" t="n">
         <v>403.5448329427017</v>
@@ -2710,6 +2736,12 @@
       </c>
       <c r="V6" s="2" t="n">
         <v>388.7214670416733</v>
+      </c>
+      <c r="W6" t="n">
+        <v>44.80088239744686</v>
+      </c>
+      <c r="X6" t="n">
+        <v>61.85648360648175</v>
       </c>
     </row>
     <row r="7">
@@ -2728,10 +2760,10 @@
         <v>19.90673338987186</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>7.380758154301324</v>
+        <v>8.406014400535831</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>9.755812879175473</v>
+        <v>11.53873959620375</v>
       </c>
       <c r="G7" s="2" t="n">
         <v>10.13479730321421</v>
@@ -2780,6 +2812,12 @@
       </c>
       <c r="V7" s="2" t="n">
         <v>9.515134778306953</v>
+      </c>
+      <c r="W7" t="n">
+        <v>8.570844148075091</v>
+      </c>
+      <c r="X7" t="n">
+        <v>11.83374639445339</v>
       </c>
     </row>
     <row r="8">
@@ -2798,10 +2836,10 @@
         <v>174.1521562345644</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>31.44683930314632</v>
+        <v>39.35749816288925</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>33.95247504464749</v>
+        <v>43.88701766727957</v>
       </c>
       <c r="G8" s="2" t="n">
         <v>72.37923796403966</v>
@@ -2850,6 +2888,12 @@
       </c>
       <c r="V8" s="2" t="n">
         <v>2184.01743144918</v>
+      </c>
+      <c r="W8" t="n">
+        <v>40.69829501237073</v>
+      </c>
+      <c r="X8" t="n">
+        <v>45.61090054732936</v>
       </c>
     </row>
     <row r="9">
@@ -2868,10 +2912,10 @@
         <v>98.07449751016838</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>21.42521366403237</v>
+        <v>26.1535868392652</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>17.87446335772178</v>
+        <v>21.83387403064396</v>
       </c>
       <c r="G9" s="2" t="n">
         <v>22.48481592273476</v>
@@ -2920,6 +2964,12 @@
       </c>
       <c r="V9" s="2" t="n">
         <v>377.6757630310734</v>
+      </c>
+      <c r="W9" t="n">
+        <v>26.94393320884064</v>
+      </c>
+      <c r="X9" t="n">
+        <v>22.49596958420992</v>
       </c>
     </row>
     <row r="10">
@@ -2938,10 +2988,10 @@
         <v>10</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>4.658907044799036</v>
+        <v>5.149566757500393</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>4.658907044799037</v>
+        <v>5.149566757500393</v>
       </c>
       <c r="G10" s="2" t="n">
         <v>5.046009141842525</v>
@@ -2991,6 +3041,12 @@
       <c r="V10" s="2" t="n">
         <v>4.830501414419818</v>
       </c>
+      <c r="W10" t="n">
+        <v>5.2271260127287</v>
+      </c>
+      <c r="X10" t="n">
+        <v>5.2271260127287</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
@@ -3059,6 +3115,12 @@
         <v>1</v>
       </c>
       <c r="V11" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1</v>
+      </c>
+      <c r="X11" t="n">
         <v>1</v>
       </c>
     </row>
@@ -3073,7 +3135,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V11"/>
+  <dimension ref="A1:X11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -3211,6 +3273,16 @@
           <t>MC_new_TE_EEfix</t>
         </is>
       </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>SPPR_1995_TEmean_catch</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>Ulanowicz_globalTEmean_catch</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
@@ -3260,19 +3332,22 @@
       <c r="O2" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="P2" t="inlineStr"/>
       <c r="Q2" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="R2" t="inlineStr"/>
       <c r="S2" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="T2" t="inlineStr"/>
       <c r="U2" s="2" t="n">
         <v>1</v>
       </c>
       <c r="V2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1</v>
+      </c>
+      <c r="X2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -3345,6 +3420,12 @@
       <c r="V3" s="2" t="n">
         <v>0.8537152806236192</v>
       </c>
+      <c r="W3" t="n">
+        <v>1</v>
+      </c>
+      <c r="X3" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
@@ -3362,10 +3443,10 @@
         <v>416.179587813214</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>56.28900254449202</v>
+        <v>73.16902902025888</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>88.59793106865003</v>
+        <v>124.051602358648</v>
       </c>
       <c r="G4" s="2" t="n">
         <v>0</v>
@@ -3414,6 +3495,12 @@
       </c>
       <c r="V4" s="2" t="n">
         <v>0</v>
+      </c>
+      <c r="W4" t="n">
+        <v>76.0908418656785</v>
+      </c>
+      <c r="X4" t="n">
+        <v>130.495353702711</v>
       </c>
     </row>
     <row r="5">
@@ -3432,10 +3519,10 @@
         <v>357.8589689857071</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>50.88677450113939</v>
+        <v>65.71390752353284</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>78.79467664999078</v>
+        <v>109.0006292271502</v>
       </c>
       <c r="G5" s="2" t="n">
         <v>1974.676817436918</v>
@@ -3484,6 +3571,12 @@
       </c>
       <c r="V5" s="2" t="n">
         <v>50303.53156474263</v>
+      </c>
+      <c r="W5" t="n">
+        <v>68.27106823443432</v>
+      </c>
+      <c r="X5" t="n">
+        <v>114.4546145406711</v>
       </c>
     </row>
     <row r="6">
@@ -3502,10 +3595,10 @@
         <v>199.0673338987186</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>34.38626616103237</v>
+        <v>43.28733232006891</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>45.45142535053177</v>
+        <v>59.41950984806437</v>
       </c>
       <c r="G6" s="2" t="n">
         <v>403.5448329427017</v>
@@ -3554,6 +3647,12 @@
       </c>
       <c r="V6" s="2" t="n">
         <v>388.7214670416733</v>
+      </c>
+      <c r="W6" t="n">
+        <v>44.80088239744686</v>
+      </c>
+      <c r="X6" t="n">
+        <v>61.85648360648175</v>
       </c>
     </row>
     <row r="7">
@@ -3572,10 +3671,10 @@
         <v>19.90673338987186</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>7.380758154301324</v>
+        <v>8.406014400535831</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>9.755812879175473</v>
+        <v>11.53873959620375</v>
       </c>
       <c r="G7" s="2" t="n">
         <v>10.13479730321421</v>
@@ -3624,6 +3723,12 @@
       </c>
       <c r="V7" s="2" t="n">
         <v>9.515134778306953</v>
+      </c>
+      <c r="W7" t="n">
+        <v>8.570844148075091</v>
+      </c>
+      <c r="X7" t="n">
+        <v>11.83374639445339</v>
       </c>
     </row>
     <row r="8">
@@ -3642,10 +3747,10 @@
         <v>174.1521562345644</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>31.44683930314632</v>
+        <v>39.35749816288925</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>33.95247504464749</v>
+        <v>43.88701766727957</v>
       </c>
       <c r="G8" s="2" t="n">
         <v>72.37923796403966</v>
@@ -3694,6 +3799,12 @@
       </c>
       <c r="V8" s="2" t="n">
         <v>2184.01743144918</v>
+      </c>
+      <c r="W8" t="n">
+        <v>40.69829501237073</v>
+      </c>
+      <c r="X8" t="n">
+        <v>45.61090054732936</v>
       </c>
     </row>
     <row r="9">
@@ -3712,10 +3823,10 @@
         <v>98.07449751016838</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>21.42521366403237</v>
+        <v>26.1535868392652</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>17.87446335772178</v>
+        <v>21.83387403064396</v>
       </c>
       <c r="G9" s="2" t="n">
         <v>22.48481592273476</v>
@@ -3764,6 +3875,12 @@
       </c>
       <c r="V9" s="2" t="n">
         <v>377.6757630310734</v>
+      </c>
+      <c r="W9" t="n">
+        <v>26.94393320884064</v>
+      </c>
+      <c r="X9" t="n">
+        <v>22.49596958420992</v>
       </c>
     </row>
     <row r="10">
@@ -3782,10 +3899,10 @@
         <v>10</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>4.658907044799036</v>
+        <v>5.149566757500393</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>4.658907044799037</v>
+        <v>5.149566757500393</v>
       </c>
       <c r="G10" s="2" t="n">
         <v>5.046009141842525</v>
@@ -3835,6 +3952,12 @@
       <c r="V10" s="2" t="n">
         <v>4.830501414419818</v>
       </c>
+      <c r="W10" t="n">
+        <v>5.2271260127287</v>
+      </c>
+      <c r="X10" t="n">
+        <v>5.2271260127287</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
@@ -3903,6 +4026,12 @@
         <v>1</v>
       </c>
       <c r="V11" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1</v>
+      </c>
+      <c r="X11" t="n">
         <v>1</v>
       </c>
     </row>
@@ -4375,7 +4504,6 @@
           <t>WARN</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr"/>
       <c r="AD2" s="2" t="n">
         <v>0.370652272914855</v>
       </c>
@@ -4501,7 +4629,6 @@
       <c r="H3" t="b">
         <v>0</v>
       </c>
-      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
           <t>Sea_of_Okhotsk_SD (1980)</t>
@@ -4565,7 +4692,6 @@
           <t>WARN</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr"/>
       <c r="AD3" s="2" t="n">
         <v>0</v>
       </c>
@@ -4605,7 +4731,6 @@
       <c r="AP3" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="AQ3" t="inlineStr"/>
       <c r="AR3" t="n">
         <v>0</v>
       </c>
@@ -4757,7 +4882,6 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr"/>
       <c r="AD4" s="2" t="n">
         <v>0.3762131611225675</v>
       </c>
@@ -4859,7 +4983,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G21"/>
+  <dimension ref="A1:G23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -4920,14 +5044,12 @@
       <c r="C2" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="D2" t="inlineStr"/>
       <c r="E2" s="2" t="n">
         <v>9496.758148000001</v>
       </c>
       <c r="F2" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="G2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
@@ -4941,14 +5063,12 @@
       <c r="C3" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="D3" t="inlineStr"/>
       <c r="E3" s="2" t="n">
         <v>9496.758148000001</v>
       </c>
       <c r="F3" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="G3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -4962,14 +5082,12 @@
       <c r="C4" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="D4" t="inlineStr"/>
       <c r="E4" s="2" t="n">
         <v>9496.758148000001</v>
       </c>
       <c r="F4" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="G4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
@@ -5393,6 +5511,50 @@
         <v>0</v>
       </c>
       <c r="G21" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>SPPR_1995_TEmean_catch</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>0</v>
+      </c>
+      <c r="C22" t="n">
+        <v>0</v>
+      </c>
+      <c r="E22" t="n">
+        <v>9496.758148000001</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Ulanowicz_globalTEmean_catch</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>0</v>
+      </c>
+      <c r="C23" t="n">
+        <v>0</v>
+      </c>
+      <c r="D23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E23" t="n">
+        <v>9496.758148000001</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5529,7 +5691,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C30"/>
+  <dimension ref="A1:C32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -5565,7 +5727,6 @@
           <t>NaN means not available, never zero. A basal source a method does not resolve is NaN, and a method that raised leaves its entire block NaN.</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
@@ -5578,7 +5739,6 @@
           <t>sppr_all, sppr_inner and sppr_PP are the same table under three source scopes, mirroring get_PPR: sppr_all sums every basal source, sppr_inner drops Import, and sppr_PP drops Import and Detritus. Each is a flat groups x methods table -- rows are group seq with the group name in the first column, one column per method, no MultiIndex. Sums are taken over each method's own basal-source columns before aggregation; the per-source breakdown itself is not written to the workbook.</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -5591,7 +5751,6 @@
           <t>SPPR_1986 and SPPR_1995 return one un-attributed SPPR column, so their value cannot be split into a PP-only part: they are NaN in sppr_PP (and in ppr_pp_only) while sppr_inner and sppr_all carry the total. A method that resolves no Detritus source (SPPR_2015) has sppr_inner equal to sppr_PP by construction.</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
@@ -5604,7 +5763,6 @@
           <t>SPPR_2015() has no only_pp_det parameter (only_pp belongs to get_PPR / get_PPR2NPP_ratio). It is called bare here and PP-only filtering is applied downstream at the get_PPR layer, which is what the ppr_pp_only column and SUM_PP already do.</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
@@ -5617,7 +5775,6 @@
           <t>Under det_open_mode='none' det_theta does not affect the recycling gain b at all (verified: identical b at theta = 1, 3 and 10). Do not read the health sheet as a theta sensitivity.</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
@@ -5630,7 +5787,6 @@
           <t>MC runs use exclude_diverged=True, so draws graded FAIL on divergence are dropped as well as draws with a negative SPPR. The two are often the same draws rather than additive -- see the mc_diagnostics sheet for the split by cause.</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
@@ -5643,7 +5799,6 @@
           <t>SPPR_EwE and the Monte-Carlo methods are called with silent=True rather than silent=False: PPRCalculator imports tqdm.notebook, whose bar needs ipywidgets and raises ImportError('IProgress not found') outside Jupyter, which makes those methods fail outright in a terminal run. Nothing is lost -- this exporter has its own progress bar, and the MC rejection counts appear in mc_diagnostics and in the run report.</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
@@ -5656,7 +5811,6 @@
           <t>diagnose_sppr grades a CONFIGURATION, not a model: a model can be healthy under one TE_option and divergent under another. Read each row with its config_ columns.</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
@@ -5669,7 +5823,6 @@
           <t>Every SPPR method, and every diagnose_sppr row, runs in a worker process with a wall-clock budget (180 s by default; --timeout SECONDS on the command line, method_timeout= from Python, and None or 0 to disable it). A method still running when the budget expires is killed and left NaN, exactly like a method that raised -- the status column of this sheet and the run report are the only places that say which of the two happened. A timeout is a statement about this machine and this model, not about the method: rerun it with a larger budget before reading anything into it.</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
@@ -5713,7 +5866,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Christensen &amp; Pauly (1995): per-group TE^(1-TL) with global_TE='mean'.</t>
+          <t>Pauly &amp; Christensen (1995): per-group TE^(1-TL) with global_TE='mean'. Arithmetic mean with consumer consumption weights.</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -5730,7 +5883,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Nullspace form of the EwE path sum, global TE at the true mean (Jensen-able on TL).</t>
+          <t>Nullspace form of the EwE path sum, global TE at the consumer consumption-weighted arithmetic mean (Jensen-able on TL).</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -6006,6 +6159,40 @@
         </is>
       </c>
       <c r="C30" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>method: SPPR_1995_TEmean_catch</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Pauly &amp; Christensen (1995): per-group TE^(1-TL) with global_TE='mean'. Arithmetic mean with consumer catch weights. Consumer biomass fallback when consumer catch is zero.</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>method: Ulanowicz_globalTEmean_catch</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Nullspace form of the EwE path sum, global TE at the consumer catch-weighted arithmetic mean. Consumer biomass fallback when consumer catch is zero (Jensen-able on TL).</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
